--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000493</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129000492</v>
       </c>
       <c r="B3" t="n">
-        <v>78802</v>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 49550-2025 artfynd.xlsx
+++ b/artfynd/A 49550-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>